--- a/Ethical_Choices_App_Full_Prompt_Library.xlsx
+++ b/Ethical_Choices_App_Full_Prompt_Library.xlsx
@@ -8,10 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="Prompts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Read Me" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Twists" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Read Me" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prompts'!$A$1:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Twists'!$A$1:$C$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +500,7 @@
     <col width="70" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="52" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -540,7 +542,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Situation (optional)</t>
+          <t>Situations</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -585,7 +587,11 @@
           <t>What are all the things you can think of that you could do?</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Waiting Room, Car Ride</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -630,7 +636,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Mealtime</t>
+          <t>Mealtime, Car Ride</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -722,7 +728,11 @@
           <t>What are all the things you can think of that you could do?</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Car Ride, Mealtime</t>
+        </is>
+      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -765,7 +775,11 @@
           <t>What are all the things you can think of that you could do?</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Mealtime, Car Ride</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -808,7 +822,11 @@
           <t>What are all the things you can think of that you could do?</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Waiting Room, Bedtime</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -851,7 +869,11 @@
           <t>What are all the things you can think of that you could do?</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Car Ride, Mealtime</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -894,7 +916,11 @@
           <t>What are all the things you can think of that you could do?</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Car Ride, Waiting Room</t>
+        </is>
+      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -937,7 +963,11 @@
           <t>What are all the things you can think of that you could do?</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Mealtime, Bedtime</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -980,7 +1010,11 @@
           <t>What are all the things you can think of that you could do?</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Car Ride, Waiting Room</t>
+        </is>
+      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1023,7 +1057,11 @@
           <t>What are all the things you can think of that you could do?</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Mealtime, Waiting Room</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1068,7 +1106,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Car Ride</t>
+          <t>Car Ride, Bedtime</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1079,7 +1117,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I13"/>
-  <dataValidations count="5">
+  <dataValidations count="4">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid value" error="Choose a value from the list (see the Read Me sheet)." type="list">
       <formula1>"3-5,6-8,9-12,13+"</formula1>
     </dataValidation>
@@ -1088,9 +1126,6 @@
     </dataValidation>
     <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid value" error="Choose a value from the list (see the Read Me sheet)." type="list">
       <formula1>"Free,Premium,Professional"</formula1>
-    </dataValidation>
-    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid value" error="Choose a value from the list (see the Read Me sheet)." type="list">
-      <formula1>"Car Ride,Bedtime,Mealtime,Waiting Room"</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a valid value" error="Choose a value from the list (see the Read Me sheet)." type="list">
       <formula1>"Yes,No"</formula1>
@@ -1106,7 +1141,661 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:C37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Prompt #</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Difficulty</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Twist Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ph-3-5-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Gentle</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>What if it was your favorite toy?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ph-3-5-001</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Deeper</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>What if the other kid was your best friend?</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ph-3-5-001</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Challenging</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>What if the other kid had waited a really long time for a turn too?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ph-3-5-002</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Gentle</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>What if no one saw it happen?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ph-3-5-002</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Deeper</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>What if the juice spilled on someone else's drawing?</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ph-3-5-002</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Challenging</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>What if a grown-up thought someone else did it?</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ph-3-5-003</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Gentle</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>What if your favorite stuffed animal was there with you?</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ph-3-5-003</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Deeper</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>What if you heard a strange noise outside?</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ph-3-5-003</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Challenging</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>What if the grown-ups were already asleep?</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>ph-6-8-001</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Gentle</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>What if a teacher was nearby?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ph-6-8-001</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Deeper</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>What if the person being mean was one of your friends?</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ph-6-8-001</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Challenging</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>What if standing up for {name} meant the mean kids might pick on you next?</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ph-6-8-002</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Gentle</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>What if your friend said it was okay?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ph-6-8-002</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Deeper</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>What if it was something your friend made by hand?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ph-6-8-002</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Challenging</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>What if no one would ever find out it was you?</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ph-6-8-003</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Gentle</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>What if one other kid was also playing alone?</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ph-6-8-003</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Deeper</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>What if the kids leaving you out were your friends yesterday?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ph-6-8-003</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Challenging</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>What if it kept happening every day for a week?</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ph-9-12-001</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Gentle</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>What if it was just a small lie?</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ph-9-12-001</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Deeper</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>What if the parents would find out anyway?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ph-9-12-001</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Challenging</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>What if your friend said they wouldn't be your friend anymore if you said no?</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>ph-9-12-002</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Gentle</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>What if it was a practice quiz that didn't count?</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>ph-9-12-002</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Deeper</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>What if the person cheating was your best friend?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>ph-9-12-002</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Challenging</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>What if the test was graded on a curve, so their cheating lowered your grade?</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>ph-9-12-003</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Gentle</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>What if the person who could help was a friend?</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>ph-9-12-003</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Deeper</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>What if {name} had already asked once and still didn't understand?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ph-9-12-003</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Challenging</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>What if asking for help meant admitting {name} had been pretending to understand?</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ph-13-15-001</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Gentle</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>What if one other person in the group seemed uncomfortable too?</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ph-13-15-001</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Deeper</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>What if everyone else in the group was already doing it?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>ph-13-15-001</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Challenging</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>What if saying no meant losing the friend group?</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>ph-13-15-002</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Gentle</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>What if {name} hadn't seen the posts yet?</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>ph-13-15-002</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Deeper</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>What if the person posting was someone you know?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>ph-13-15-002</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Challenging</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>What if speaking up meant the posts might start being about you?</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>ph-13-15-003</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Gentle</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>What if the decision was about your weekend plans?</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>ph-13-15-003</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Deeper</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>What if your brother or sister agreed with your parents?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>ph-13-15-003</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Challenging</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>What if your parents had a good reason they hadn't told you yet?</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C37"/>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Not a valid value" error="Choose Gentle, Deeper or Challenging." type="list">
+      <formula1>"Gentle,Deeper,Challenging"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1280,12 +1969,12 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Situation (optional)</t>
+          <t>Situations</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>App-only: the moment it suits — Car Ride, Bedtime, Mealtime, Waiting Room — or blank for anywhere.</t>
+          <t>App-only: the moments it suits, comma-separated, from: Car Ride, Bedtime, Mealtime, Waiting Room. Every prompt should have at least one. Prompts also always appear under "Anywhere".</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1997,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Personalization tokens</t>
+          <t>Twists sheet</t>
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
@@ -1316,10 +2005,58 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
+          <t>What a twist is</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>A follow-up "What if…?" that changes the scenario, shown when the card is flipped over. One row per twist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Prompt #</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>The # of the prompt it belongs to (from the Prompts sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Difficulty</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Gentle, Deeper or Challenging (dropdown). Every prompt needs at least one of each.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Personalization tokens</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
           <t>{name} {location} {interest}</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Optional. The app fills these from the Personalize screen (e.g. "What if {name} was struggling…"), or uses a neutral fallback such as "a friend".</t>
         </is>
